--- a/tests/ProcessCore.Tests/TestObjects/ruch_proteomics_datamap.xlsx
+++ b/tests/ProcessCore.Tests/TestObjects/ruch_proteomics_datamap.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7020B3F9-A470-475D-BAB1-AA6BAFA1DFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="25510" yWindow="0" windowWidth="25780" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="isa_datamap" state="visible" r:id="rId4"/>
+    <sheet name="isa_datamap" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="34">
   <si>
     <t>Data</t>
   </si>
@@ -110,19 +114,22 @@
   </si>
   <si>
     <t>NCIT:C45255</t>
+  </si>
+  <si>
+    <t>Label</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,8 +172,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="datamapTable" displayName="datamapTable" ref="A1:N4" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A1:N4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="datamapTable" displayName="datamapTable" ref="A1:O4">
+  <autoFilter ref="A1:O4" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -181,22 +188,24 @@
     <filterColumn colId="11" hiddenButton="1"/>
     <filterColumn colId="12" hiddenButton="1"/>
     <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="14">
-    <tableColumn id="1" name="Data" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Data Format" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Data Selector Format" totalsRowFunction="none"/>
-    <tableColumn id="4" name="Explication" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Term Source REF" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Term Accession Number" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Unit" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Term Source REF " totalsRowFunction="none"/>
-    <tableColumn id="9" name="Term Accession Number " totalsRowFunction="none"/>
-    <tableColumn id="10" name="Object Type" totalsRowFunction="none"/>
-    <tableColumn id="11" name="Term Source REF  " totalsRowFunction="none"/>
-    <tableColumn id="12" name="Term Accession Number  " totalsRowFunction="none"/>
-    <tableColumn id="13" name="Description" totalsRowFunction="none"/>
-    <tableColumn id="14" name="Generated By" totalsRowFunction="none"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Data" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Data Format"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Data Selector Format"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Explication"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Term Source REF"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Term Accession Number"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Unit"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Term Source REF "/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Term Accession Number "/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Object Type"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Term Source REF  "/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Term Accession Number  "/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Description"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Generated By"/>
+    <tableColumn id="15" xr3:uid="{5678A3F6-2DA2-4815-A366-404AB9151774}" name="Label"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -498,11 +507,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -545,8 +570,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -590,7 +618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -634,7 +662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -680,7 +708,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
